--- a/Dashboards/data/Data final/ingresos/inglab_educacion.xlsx
+++ b/Dashboards/data/Data final/ingresos/inglab_educacion.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>345.06</v>
+        <v>343.25</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>803.25</v>
+        <v>830.28</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>369.51</v>
+        <v>376.68</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>838.34</v>
+        <v>851.24</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>374.84</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>829.02</v>
+        <v>804.46</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>381.67</v>
+        <v>379.47</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>824.48</v>
+        <v>788.23</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>400.93</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>851.75</v>
+        <v>932.22</v>
       </c>
     </row>
   </sheetData>
